--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\GenAI Course\playwright-whatsapp-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E73B57D-A32A-4A9B-9661-EB3CA8FA125C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA0D92F-E06D-455E-992A-A4C39A4B39B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,37 +25,28 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Screenshot</t>
-  </si>
-  <si>
-    <t>Error</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Ramesh</t>
   </si>
   <si>
     <t>Wife Priya</t>
   </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>message</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,6 +61,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0F1115"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -92,11 +89,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,29 +381,23 @@
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>9962561504</v>
@@ -413,7 +405,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>8682930172</v>

--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -2,71 +2,69 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\GenAI Course\playwright-whatsapp-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA0D92F-E06D-455E-992A-A4C39A4B39B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAB2A46-CD6A-4F70-B8C3-3F68A07CB998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4030D962-6643-40B0-9EA0-EF2FD3336B5D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Ramesh</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>How was your day?</t>
   </si>
   <si>
     <t>Wife Priya</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>message</t>
+    <t>second message - How was your day?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF0F1115"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -89,12 +87,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -113,9 +107,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -129,7 +123,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -141,7 +135,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -153,7 +147,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -188,6 +182,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -223,9 +234,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -367,48 +395,52 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0302F508-EC43-4D8F-B95C-2E8A45AC1EF9}">
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>8682930172</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>9962561504</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
       </c>
       <c r="B3">
         <v>8682930172</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
